--- a/reports/snowbowl_Report_20251216.xlsx
+++ b/reports/snowbowl_Report_20251216.xlsx
@@ -37,8 +37,8 @@
 Dec 15 - Dec 16</t>
   </si>
   <si>
-    <t>For The Week Ending (Actual) (Budget)
-Dec 15 - Dec 16</t>
+    <t>Week Total (Actual) (Budget)
+Dec 15 - Dec 21</t>
   </si>
   <si>
     <t>For The Week Ending (Prior Year)
@@ -1075,10 +1075,10 @@
         <v>78</v>
       </c>
       <c r="E6" s="4">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F6" s="4">
-        <v>250</v>
+        <v>975</v>
       </c>
       <c r="G6" s="4">
         <v>161</v>
@@ -1087,7 +1087,7 @@
         <v>1105</v>
       </c>
       <c r="I6" s="4">
-        <v>1853</v>
+        <v>1851</v>
       </c>
       <c r="J6" s="4">
         <v>1275</v>
@@ -1096,7 +1096,7 @@
         <v>1270</v>
       </c>
       <c r="L6" s="4">
-        <v>3790</v>
+        <v>3788</v>
       </c>
       <c r="M6" s="4">
         <v>1875</v>
@@ -1122,7 +1122,7 @@
         <v>1425</v>
       </c>
       <c r="F7" s="4">
-        <v>1100</v>
+        <v>4800</v>
       </c>
       <c r="G7" s="4">
         <v>1283</v>
@@ -1166,7 +1166,7 @@
         <v>2805</v>
       </c>
       <c r="F8" s="4">
-        <v>2500</v>
+        <v>9000</v>
       </c>
       <c r="G8" s="4">
         <v>2251</v>
@@ -1175,7 +1175,7 @@
         <v>8806</v>
       </c>
       <c r="I8" s="4">
-        <v>18331</v>
+        <v>18330</v>
       </c>
       <c r="J8" s="4">
         <v>14300</v>
@@ -1184,7 +1184,7 @@
         <v>13231</v>
       </c>
       <c r="L8" s="4">
-        <v>30319</v>
+        <v>30315</v>
       </c>
       <c r="M8" s="4">
         <v>19200</v>
@@ -1251,10 +1251,10 @@
         <v>1886</v>
       </c>
       <c r="E10" s="4">
-        <v>4623</v>
+        <v>4621</v>
       </c>
       <c r="F10" s="4">
-        <v>3850</v>
+        <v>14775</v>
       </c>
       <c r="G10" s="4">
         <v>3764</v>
@@ -1263,7 +1263,7 @@
         <v>16259</v>
       </c>
       <c r="I10" s="4">
-        <v>36863</v>
+        <v>36860</v>
       </c>
       <c r="J10" s="4">
         <v>24475</v>
@@ -1272,7 +1272,7 @@
         <v>26331</v>
       </c>
       <c r="L10" s="4">
-        <v>66631</v>
+        <v>66625</v>
       </c>
       <c r="M10" s="4">
         <v>36900</v>
@@ -1347,13 +1347,13 @@
         <v>1823</v>
       </c>
       <c r="F14" s="4">
-        <v>1823.44</v>
+        <v>6382.04</v>
       </c>
       <c r="G14" s="4">
         <v>1794.54</v>
       </c>
       <c r="H14" s="4">
-        <v>7178.16</v>
+        <v>6280.89</v>
       </c>
       <c r="I14" s="4">
         <v>14584</v>
@@ -1479,16 +1479,16 @@
         <v>10725.09184722222</v>
       </c>
       <c r="F17" s="4">
-        <v>9814.68</v>
+        <v>37501.36</v>
       </c>
       <c r="G17" s="4">
         <v>9001.98</v>
       </c>
       <c r="H17" s="4">
-        <v>41477.58</v>
+        <v>35456.43</v>
       </c>
       <c r="I17" s="4">
-        <v>88665.65115277778</v>
+        <v>88665.65115277775</v>
       </c>
       <c r="J17" s="4">
         <v>57328.96</v>
@@ -1497,7 +1497,7 @@
         <v>62757.62</v>
       </c>
       <c r="L17" s="4">
-        <v>154248.7972916666</v>
+        <v>154248.7972916665</v>
       </c>
       <c r="M17" s="4">
         <v>86010.34</v>
@@ -1599,7 +1599,7 @@
         <v>30</v>
       </c>
       <c r="B20" s="4">
-        <v>724.077888888889</v>
+        <v>948.2210000000001</v>
       </c>
       <c r="C20" s="4">
         <v>1191.77</v>
@@ -1608,19 +1608,19 @@
         <v>1136.12</v>
       </c>
       <c r="E20" s="4">
-        <v>1671.804777777778</v>
+        <v>1895.947888888889</v>
       </c>
       <c r="F20" s="4">
-        <v>2347.04</v>
+        <v>8555.190000000001</v>
       </c>
       <c r="G20" s="4">
         <v>2262.22</v>
       </c>
       <c r="H20" s="4">
-        <v>10260.4</v>
+        <v>9117.469999999999</v>
       </c>
       <c r="I20" s="4">
-        <v>18653.433175</v>
+        <v>18877.57628611111</v>
       </c>
       <c r="J20" s="4">
         <v>19457.42</v>
@@ -1629,7 +1629,7 @@
         <v>20634.43</v>
       </c>
       <c r="L20" s="4">
-        <v>55471.75628888889</v>
+        <v>55695.89939999999</v>
       </c>
       <c r="M20" s="4">
         <v>54927.32</v>
@@ -1731,7 +1731,7 @@
         <v>33</v>
       </c>
       <c r="B23" s="4">
-        <v>1315.027513888889</v>
+        <v>1517.459458333333</v>
       </c>
       <c r="C23" s="4">
         <v>2522.72</v>
@@ -1740,19 +1740,19 @@
         <v>1942.14</v>
       </c>
       <c r="E23" s="4">
-        <v>3666.786222222222</v>
+        <v>3869.218166666667</v>
       </c>
       <c r="F23" s="4">
-        <v>5045.44</v>
+        <v>14474.06</v>
       </c>
       <c r="G23" s="4">
         <v>3776.2</v>
       </c>
       <c r="H23" s="4">
-        <v>12538.69</v>
+        <v>11109.54</v>
       </c>
       <c r="I23" s="4">
-        <v>43308.06718055556</v>
+        <v>43510.49912500001</v>
       </c>
       <c r="J23" s="4">
         <v>33993.56</v>
@@ -1761,7 +1761,7 @@
         <v>35754.36</v>
       </c>
       <c r="L23" s="4">
-        <v>120842.6067083333</v>
+        <v>121045.0386527779</v>
       </c>
       <c r="M23" s="4">
         <v>117395.28</v>
@@ -1875,16 +1875,16 @@
         <v>1396.141902777778</v>
       </c>
       <c r="F26" s="4">
-        <v>1719.68</v>
+        <v>5333.32</v>
       </c>
       <c r="G26" s="4">
         <v>608.17</v>
       </c>
       <c r="H26" s="4">
-        <v>4002.8</v>
+        <v>3520.7</v>
       </c>
       <c r="I26" s="4">
-        <v>12290.72655555555</v>
+        <v>12290.72655555556</v>
       </c>
       <c r="J26" s="4">
         <v>9973.68</v>
@@ -2007,13 +2007,13 @@
         <v>820.1992083333332</v>
       </c>
       <c r="F29" s="4">
-        <v>2887.02</v>
+        <v>9718.700000000001</v>
       </c>
       <c r="G29" s="4">
         <v>1665.19</v>
       </c>
       <c r="H29" s="4">
-        <v>6735.35</v>
+        <v>5779.42</v>
       </c>
       <c r="I29" s="4">
         <v>12053.41377777778</v>
@@ -2139,16 +2139,16 @@
         <v>1144.461944444444</v>
       </c>
       <c r="F32" s="4">
-        <v>1900</v>
+        <v>4560</v>
       </c>
       <c r="G32" s="4">
         <v>1532.66</v>
       </c>
       <c r="H32" s="4">
-        <v>5150.56</v>
+        <v>4284.04</v>
       </c>
       <c r="I32" s="4">
-        <v>9505.479999999996</v>
+        <v>9505.48</v>
       </c>
       <c r="J32" s="4">
         <v>11020</v>
@@ -2271,16 +2271,16 @@
         <v>5958.221402777778</v>
       </c>
       <c r="F35" s="4">
-        <v>4945.74</v>
+        <v>19142.74</v>
       </c>
       <c r="G35" s="4">
         <v>5573.19</v>
       </c>
       <c r="H35" s="4">
-        <v>23446.96</v>
+        <v>20464.21</v>
       </c>
       <c r="I35" s="4">
-        <v>50578.23681944443</v>
+        <v>50578.23681944444</v>
       </c>
       <c r="J35" s="4">
         <v>32147.42</v>
@@ -2289,7 +2289,7 @@
         <v>40285.65</v>
       </c>
       <c r="L35" s="4">
-        <v>115803.9545694444</v>
+        <v>115803.9545694445</v>
       </c>
       <c r="M35" s="4">
         <v>77319.17</v>
@@ -2359,7 +2359,7 @@
         <v>117931.17</v>
       </c>
       <c r="F37" s="4">
-        <v>185929</v>
+        <v>770884</v>
       </c>
       <c r="G37" s="4">
         <v>96012.33</v>
@@ -2403,13 +2403,13 @@
         <v>3082.734277777778</v>
       </c>
       <c r="F38" s="4">
-        <v>2948.5</v>
+        <v>12558.03</v>
       </c>
       <c r="G38" s="4">
         <v>3382.3</v>
       </c>
       <c r="H38" s="4">
-        <v>16468.52</v>
+        <v>14059.57</v>
       </c>
       <c r="I38" s="4">
         <v>31518.67583333333</v>
@@ -2447,16 +2447,16 @@
         <v>3825.537959924719</v>
       </c>
       <c r="F39" s="5">
-        <v>6305.884347973546</v>
+        <v>6138.574282749762</v>
       </c>
       <c r="G39" s="5">
         <v>2838.66984004967</v>
       </c>
       <c r="H39" s="5">
-        <v>3354.74049884264</v>
+        <v>3929.537745464477</v>
       </c>
       <c r="I39" s="5">
-        <v>4223.336180234517</v>
+        <v>4223.336180234518</v>
       </c>
       <c r="J39" s="5">
         <v>5025.734464270849</v>
@@ -2491,7 +2491,7 @@
         <v>21146.75</v>
       </c>
       <c r="F40" s="4">
-        <v>45585</v>
+        <v>181468</v>
       </c>
       <c r="G40" s="4">
         <v>4488.39</v>
@@ -2535,13 +2535,13 @@
         <v>2445.217458333334</v>
       </c>
       <c r="F41" s="4">
-        <v>11130.84</v>
+        <v>45074.77</v>
       </c>
       <c r="G41" s="4">
         <v>6333.86</v>
       </c>
       <c r="H41" s="4">
-        <v>129717.04</v>
+        <v>124717.64</v>
       </c>
       <c r="I41" s="4">
         <v>27219.65143055558</v>
@@ -2553,7 +2553,7 @@
         <v>88163.69</v>
       </c>
       <c r="L41" s="4">
-        <v>76256.41170833335</v>
+        <v>76256.41170833333</v>
       </c>
       <c r="M41" s="4">
         <v>105188.8</v>
@@ -2579,13 +2579,13 @@
         <v>864.8208333345403</v>
       </c>
       <c r="F42" s="5">
-        <v>409.5378246385717</v>
+        <v>402.5932911027611</v>
       </c>
       <c r="G42" s="5">
         <v>70.86342293640845</v>
       </c>
       <c r="H42" s="5">
-        <v>46.7911309107886</v>
+        <v>48.66678843506019</v>
       </c>
       <c r="I42" s="5">
         <v>573.4312961288871</v>
@@ -2597,7 +2597,7 @@
         <v>55.06086462578869</v>
       </c>
       <c r="L42" s="5">
-        <v>269.0719316623408</v>
+        <v>269.0719316623409</v>
       </c>
       <c r="M42" s="5">
         <v>171.4906910241395</v>
@@ -2623,7 +2623,7 @@
         <v>48390.08</v>
       </c>
       <c r="F43" s="4">
-        <v>69595</v>
+        <v>289398</v>
       </c>
       <c r="G43" s="4">
         <v>45546.49</v>
@@ -2667,16 +2667,16 @@
         <v>4112.504777777778</v>
       </c>
       <c r="F44" s="4">
-        <v>3711.2</v>
+        <v>14561.95</v>
       </c>
       <c r="G44" s="4">
         <v>4455.39</v>
       </c>
       <c r="H44" s="4">
-        <v>21154.4</v>
+        <v>18266.51</v>
       </c>
       <c r="I44" s="4">
-        <v>28549.44151388888</v>
+        <v>28549.4415138889</v>
       </c>
       <c r="J44" s="4">
         <v>23045.65</v>
@@ -2685,7 +2685,7 @@
         <v>28812.93</v>
       </c>
       <c r="L44" s="4">
-        <v>49342.22398611104</v>
+        <v>49342.22398611109</v>
       </c>
       <c r="M44" s="4">
         <v>48976.12</v>
@@ -2711,16 +2711,16 @@
         <v>1176.657113238612</v>
       </c>
       <c r="F45" s="5">
-        <v>1875.269454623841</v>
+        <v>1987.357462427766</v>
       </c>
       <c r="G45" s="5">
         <v>1022.278408848608</v>
       </c>
       <c r="H45" s="5">
-        <v>1005.790332034943</v>
+        <v>1164.803293020944</v>
       </c>
       <c r="I45" s="5">
-        <v>1399.149156055028</v>
+        <v>1399.149156055027</v>
       </c>
       <c r="J45" s="5">
         <v>1340.062007363646</v>
@@ -2729,7 +2729,7 @@
         <v>943.4436900377714</v>
       </c>
       <c r="L45" s="5">
-        <v>1117.08821668669</v>
+        <v>1117.088216686689</v>
       </c>
       <c r="M45" s="5">
         <v>822.1271917824442</v>
@@ -2755,7 +2755,7 @@
         <v>0</v>
       </c>
       <c r="F46" s="4">
-        <v>1709</v>
+        <v>5819</v>
       </c>
       <c r="G46" s="4">
         <v>0</v>
@@ -2799,16 +2799,16 @@
         <v>481.3897916666666</v>
       </c>
       <c r="F47" s="4">
-        <v>620.25</v>
+        <v>2495</v>
       </c>
       <c r="G47" s="4">
         <v>791.1</v>
       </c>
       <c r="H47" s="4">
-        <v>2793.06</v>
+        <v>2526.83</v>
       </c>
       <c r="I47" s="4">
-        <v>5631.892375000002</v>
+        <v>5631.892374999999</v>
       </c>
       <c r="J47" s="4">
         <v>5546.75</v>
@@ -2817,7 +2817,7 @@
         <v>5985.84</v>
       </c>
       <c r="L47" s="4">
-        <v>10366.23980555556</v>
+        <v>10366.23980555555</v>
       </c>
       <c r="M47" s="4">
         <v>13573.8</v>
@@ -2843,7 +2843,7 @@
         <v>0</v>
       </c>
       <c r="F48" s="5">
-        <v>275.534058847239</v>
+        <v>233.2264529058116</v>
       </c>
       <c r="G48" s="5">
         <v>0</v>
@@ -2887,7 +2887,7 @@
         <v>0</v>
       </c>
       <c r="F49" s="4">
-        <v>1375.08</v>
+        <v>6773.65</v>
       </c>
       <c r="G49" s="4">
         <v>0</v>
@@ -2931,13 +2931,13 @@
         <v>449.529125</v>
       </c>
       <c r="F50" s="4">
-        <v>364.32</v>
+        <v>1275.12</v>
       </c>
       <c r="G50" s="4">
         <v>316.32</v>
       </c>
       <c r="H50" s="4">
-        <v>1410.99</v>
+        <v>1233.55</v>
       </c>
       <c r="I50" s="4">
         <v>1652.150333333333</v>
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="F51" s="5">
-        <v>377.4374176548089</v>
+        <v>531.2166698036264</v>
       </c>
       <c r="G51" s="5">
         <v>0</v>
@@ -3019,7 +3019,7 @@
         <v>18747.01</v>
       </c>
       <c r="F52" s="4">
-        <v>17788.51</v>
+        <v>83168.07000000001</v>
       </c>
       <c r="G52" s="4">
         <v>12097.35</v>
@@ -3063,13 +3063,13 @@
         <v>1446.832819444445</v>
       </c>
       <c r="F53" s="4">
-        <v>1119.95</v>
+        <v>3644.05</v>
       </c>
       <c r="G53" s="4">
         <v>1404.8</v>
       </c>
       <c r="H53" s="4">
-        <v>5457.18</v>
+        <v>4272.03</v>
       </c>
       <c r="I53" s="4">
         <v>11136.27808333334</v>
@@ -3107,13 +3107,13 @@
         <v>1295.72745019694</v>
       </c>
       <c r="F54" s="5">
-        <v>1588.330729050404</v>
+        <v>2282.297718198159</v>
       </c>
       <c r="G54" s="5">
         <v>861.1439350797267</v>
       </c>
       <c r="H54" s="5">
-        <v>1063.04996353428</v>
+        <v>1357.962139778981</v>
       </c>
       <c r="I54" s="5">
         <v>1326.036031921706</v>
@@ -3125,7 +3125,7 @@
         <v>834.0750261446124</v>
       </c>
       <c r="L54" s="5">
-        <v>1150.228597440576</v>
+        <v>1150.228597440577</v>
       </c>
       <c r="M54" s="5">
         <v>923.6067155242353</v>
@@ -3151,7 +3151,7 @@
         <v>15.43</v>
       </c>
       <c r="F55" s="4">
-        <v>376.99</v>
+        <v>1502.91</v>
       </c>
       <c r="G55" s="4">
         <v>0</v>
@@ -3195,13 +3195,13 @@
         <v>0</v>
       </c>
       <c r="F56" s="4">
-        <v>309</v>
+        <v>1429.14</v>
       </c>
       <c r="G56" s="4">
         <v>294.88</v>
       </c>
       <c r="H56" s="4">
-        <v>1857.15</v>
+        <v>1537.7</v>
       </c>
       <c r="I56" s="4">
         <v>1093.355805555556</v>
@@ -3213,7 +3213,7 @@
         <v>2382.39</v>
       </c>
       <c r="L56" s="4">
-        <v>4469.940055555556</v>
+        <v>4469.940055555555</v>
       </c>
       <c r="M56" s="4">
         <v>7107</v>
@@ -3239,13 +3239,13 @@
         <v>0</v>
       </c>
       <c r="F57" s="5">
-        <v>122.0032362459547</v>
+        <v>105.161845585457</v>
       </c>
       <c r="G57" s="5">
         <v>0</v>
       </c>
       <c r="H57" s="5">
-        <v>2.410144576367014</v>
+        <v>2.910840866228783</v>
       </c>
       <c r="I57" s="5">
         <v>5.996218217974127</v>
@@ -3257,7 +3257,7 @@
         <v>0</v>
       </c>
       <c r="L57" s="5">
-        <v>4.417508904947905</v>
+        <v>4.417508904947906</v>
       </c>
       <c r="M57" s="5">
         <v>48.04010130856901</v>
@@ -3327,13 +3327,13 @@
         <v>2425.171055555556</v>
       </c>
       <c r="F59" s="4">
-        <v>1827.42</v>
+        <v>6395.97</v>
       </c>
       <c r="G59" s="4">
         <v>1857.06</v>
       </c>
       <c r="H59" s="4">
-        <v>7428.24</v>
+        <v>6499.71</v>
       </c>
       <c r="I59" s="4">
         <v>18825.82231944445</v>
@@ -3415,7 +3415,7 @@
         <v>15562.55</v>
       </c>
       <c r="F61" s="4">
-        <v>14691.6</v>
+        <v>56381.4</v>
       </c>
       <c r="G61" s="4">
         <v>13374.02</v>
@@ -3459,16 +3459,16 @@
         <v>3035.584236111111</v>
       </c>
       <c r="F62" s="4">
-        <v>1856.24</v>
+        <v>7958.19</v>
       </c>
       <c r="G62" s="4">
         <v>2392.64</v>
       </c>
       <c r="H62" s="4">
-        <v>10328</v>
+        <v>8888.07</v>
       </c>
       <c r="I62" s="4">
-        <v>28158.47826388888</v>
+        <v>28158.47826388889</v>
       </c>
       <c r="J62" s="4">
         <v>15877.34</v>
@@ -3477,7 +3477,7 @@
         <v>17688.1</v>
       </c>
       <c r="L62" s="4">
-        <v>54917.99131944444</v>
+        <v>54917.99131944447</v>
       </c>
       <c r="M62" s="4">
         <v>41735.52</v>
@@ -3491,7 +3491,7 @@
         <v>73</v>
       </c>
       <c r="B63" s="5">
-        <v>480.7783774017063</v>
+        <v>480.7783774017065</v>
       </c>
       <c r="C63" s="5">
         <v>770.9132439770718</v>
@@ -3503,16 +3503,16 @@
         <v>512.6706686267812</v>
       </c>
       <c r="F63" s="5">
-        <v>791.4709304831272</v>
+        <v>708.4701420800459</v>
       </c>
       <c r="G63" s="5">
         <v>558.9649926441086</v>
       </c>
       <c r="H63" s="5">
-        <v>598.641750580945</v>
+        <v>695.6259345392195</v>
       </c>
       <c r="I63" s="5">
-        <v>515.1983308204688</v>
+        <v>515.1983308204686</v>
       </c>
       <c r="J63" s="5">
         <v>588.2383321135657</v>
@@ -3521,7 +3521,7 @@
         <v>620.5557408653276</v>
       </c>
       <c r="L63" s="5">
-        <v>552.6664262619108</v>
+        <v>552.6664262619105</v>
       </c>
       <c r="M63" s="5">
         <v>337.3874340130421</v>
@@ -3547,7 +3547,7 @@
         <v>36065.84</v>
       </c>
       <c r="F64" s="4">
-        <v>28062.02</v>
+        <v>107692.56</v>
       </c>
       <c r="G64" s="4">
         <v>21492.2</v>
@@ -3588,16 +3588,16 @@
         <v>1333.62</v>
       </c>
       <c r="E65" s="4">
-        <v>5440.200958333332</v>
+        <v>5440.200958333333</v>
       </c>
       <c r="F65" s="4">
-        <v>4090.96</v>
+        <v>15613.78</v>
       </c>
       <c r="G65" s="4">
         <v>2949.3</v>
       </c>
       <c r="H65" s="4">
-        <v>17185.2</v>
+        <v>14604.92</v>
       </c>
       <c r="I65" s="4">
         <v>38729.5486388889</v>
@@ -3609,7 +3609,7 @@
         <v>27796.67</v>
       </c>
       <c r="L65" s="4">
-        <v>61798.38701388889</v>
+        <v>61798.3870138889</v>
       </c>
       <c r="M65" s="4">
         <v>48945.95</v>
@@ -3635,16 +3635,16 @@
         <v>662.9505100313276</v>
       </c>
       <c r="F66" s="5">
-        <v>685.9519525979232</v>
+        <v>689.7276636407071</v>
       </c>
       <c r="G66" s="5">
         <v>728.7220696436442</v>
       </c>
       <c r="H66" s="5">
-        <v>612.3503363359169</v>
+        <v>720.535477085804</v>
       </c>
       <c r="I66" s="5">
-        <v>609.0340019174748</v>
+        <v>609.0340019174749</v>
       </c>
       <c r="J66" s="5">
         <v>631.7062245242309</v>
@@ -3679,7 +3679,7 @@
         <v>1203.23</v>
       </c>
       <c r="F67" s="4">
-        <v>2078.52</v>
+        <v>7274.82</v>
       </c>
       <c r="G67" s="4">
         <v>1435.2</v>
@@ -3720,19 +3720,19 @@
         <v>256.29</v>
       </c>
       <c r="E68" s="4">
-        <v>862.3189444444445</v>
+        <v>862.3189444444444</v>
       </c>
       <c r="F68" s="4">
-        <v>602.6</v>
+        <v>2877.57</v>
       </c>
       <c r="G68" s="4">
         <v>712.1900000000001</v>
       </c>
       <c r="H68" s="4">
-        <v>3253.57</v>
+        <v>2978.08</v>
       </c>
       <c r="I68" s="4">
-        <v>6783.890388888888</v>
+        <v>6783.890388888889</v>
       </c>
       <c r="J68" s="4">
         <v>6357.74</v>
@@ -3741,7 +3741,7 @@
         <v>5924.37</v>
       </c>
       <c r="L68" s="4">
-        <v>17967.39305555555</v>
+        <v>17967.39305555556</v>
       </c>
       <c r="M68" s="4">
         <v>17124.17</v>
@@ -3767,16 +3767,16 @@
         <v>139.5342184874751</v>
       </c>
       <c r="F69" s="5">
-        <v>344.9253235977431</v>
+        <v>252.8112261387212</v>
       </c>
       <c r="G69" s="5">
         <v>201.5192575015094</v>
       </c>
       <c r="H69" s="5">
-        <v>176.4369600162283</v>
+        <v>192.7584215333369</v>
       </c>
       <c r="I69" s="5">
-        <v>201.3822337456367</v>
+        <v>201.3822337456366</v>
       </c>
       <c r="J69" s="5">
         <v>261.5419944823161</v>
@@ -3785,7 +3785,7 @@
         <v>216.764482974561</v>
       </c>
       <c r="L69" s="5">
-        <v>209.0326620220906</v>
+        <v>209.0326620220905</v>
       </c>
       <c r="M69" s="5">
         <v>240.2677618827657</v>
@@ -3811,7 +3811,7 @@
         <v>2169.23</v>
       </c>
       <c r="F70" s="4">
-        <v>0</v>
+        <v>9564.280000000001</v>
       </c>
       <c r="G70" s="4">
         <v>0</v>
@@ -3855,16 +3855,16 @@
         <v>974.2639722222222</v>
       </c>
       <c r="F71" s="4">
-        <v>1114.04</v>
+        <v>3548.94</v>
       </c>
       <c r="G71" s="4">
         <v>110.82</v>
       </c>
       <c r="H71" s="4">
-        <v>1297.85</v>
+        <v>1021.49</v>
       </c>
       <c r="I71" s="4">
-        <v>8036.559402777777</v>
+        <v>8036.559402777775</v>
       </c>
       <c r="J71" s="4">
         <v>3921.81</v>
@@ -3873,7 +3873,7 @@
         <v>0</v>
       </c>
       <c r="L71" s="4">
-        <v>8502.661499999997</v>
+        <v>8502.661500000002</v>
       </c>
       <c r="M71" s="4">
         <v>3921.81</v>
@@ -3899,16 +3899,16 @@
         <v>222.6532091761693</v>
       </c>
       <c r="F72" s="5">
-        <v>0</v>
+        <v>269.49680749745</v>
       </c>
       <c r="G72" s="5">
         <v>0</v>
       </c>
       <c r="H72" s="5">
-        <v>267.4908502523405</v>
+        <v>339.8594210418115</v>
       </c>
       <c r="I72" s="5">
-        <v>173.8959335654205</v>
+        <v>173.8959335654206</v>
       </c>
       <c r="J72" s="5">
         <v>0</v>
@@ -3917,7 +3917,7 @@
         <v>0</v>
       </c>
       <c r="L72" s="5">
-        <v>164.4632095491512</v>
+        <v>164.4632095491511</v>
       </c>
       <c r="M72" s="5">
         <v>0</v>
@@ -4125,7 +4125,7 @@
         <v>0</v>
       </c>
       <c r="H77" s="4">
-        <v>136.5</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I77" s="4">
         <v>0</v>
@@ -4207,7 +4207,7 @@
         <v>0</v>
       </c>
       <c r="F79" s="4">
-        <v>3235.66</v>
+        <v>19171.36</v>
       </c>
       <c r="G79" s="4">
         <v>0</v>
@@ -4251,16 +4251,16 @@
         <v>1006.549708333333</v>
       </c>
       <c r="F80" s="4">
-        <v>1075.28</v>
+        <v>4085.08</v>
       </c>
       <c r="G80" s="4">
         <v>1071.6</v>
       </c>
       <c r="H80" s="4">
-        <v>4264.87</v>
+        <v>3741.55</v>
       </c>
       <c r="I80" s="4">
-        <v>8639.003611111111</v>
+        <v>8639.003611111109</v>
       </c>
       <c r="J80" s="4">
         <v>9245.440000000001</v>
@@ -4269,7 +4269,7 @@
         <v>8788.209999999999</v>
       </c>
       <c r="L80" s="4">
-        <v>20860.45558333333</v>
+        <v>20860.45558333332</v>
       </c>
       <c r="M80" s="4">
         <v>25006.24</v>
@@ -4295,7 +4295,7 @@
         <v>0</v>
       </c>
       <c r="F81" s="5">
-        <v>300.9132505021947</v>
+        <v>469.3019475750781</v>
       </c>
       <c r="G81" s="5">
         <v>0</v>
@@ -4383,13 +4383,13 @@
         <v>1041.945</v>
       </c>
       <c r="F83" s="4">
-        <v>581.64</v>
+        <v>2157.44</v>
       </c>
       <c r="G83" s="4">
         <v>542.41</v>
       </c>
       <c r="H83" s="4">
-        <v>2579.3</v>
+        <v>2218.8</v>
       </c>
       <c r="I83" s="4">
         <v>6357.183083333335</v>
@@ -4515,13 +4515,13 @@
         <v>500</v>
       </c>
       <c r="F86" s="4">
-        <v>500.12</v>
+        <v>1750.42</v>
       </c>
       <c r="G86" s="4">
         <v>417.16</v>
       </c>
       <c r="H86" s="4">
-        <v>1668.64</v>
+        <v>1460.06</v>
       </c>
       <c r="I86" s="4">
         <v>4000</v>
@@ -4647,16 +4647,16 @@
         <v>762.0536527777779</v>
       </c>
       <c r="F89" s="4">
-        <v>945.54</v>
+        <v>3905.51</v>
       </c>
       <c r="G89" s="4">
         <v>1519.74</v>
       </c>
       <c r="H89" s="4">
-        <v>4819.93</v>
+        <v>3837.62</v>
       </c>
       <c r="I89" s="4">
-        <v>6355.972722222223</v>
+        <v>6355.972722222224</v>
       </c>
       <c r="J89" s="4">
         <v>5840.37</v>
@@ -4779,13 +4779,13 @@
         <v>818.0666666666666</v>
       </c>
       <c r="F92" s="4">
-        <v>1012.88</v>
+        <v>3260.55</v>
       </c>
       <c r="G92" s="4">
         <v>581.46</v>
       </c>
       <c r="H92" s="4">
-        <v>3442.34</v>
+        <v>2449.84</v>
       </c>
       <c r="I92" s="4">
         <v>8982.896999999999</v>
@@ -4899,7 +4899,7 @@
         <v>105</v>
       </c>
       <c r="B95" s="4">
-        <v>687.7275555555556</v>
+        <v>687.7275555555555</v>
       </c>
       <c r="C95" s="4">
         <v>724.1900000000001</v>
@@ -4911,16 +4911,16 @@
         <v>1740.888347222222</v>
       </c>
       <c r="F95" s="4">
-        <v>1448.38</v>
+        <v>6490.85</v>
       </c>
       <c r="G95" s="4">
         <v>1721.51</v>
       </c>
       <c r="H95" s="4">
-        <v>7200.32</v>
+        <v>6359.67</v>
       </c>
       <c r="I95" s="4">
-        <v>14767.19366666666</v>
+        <v>14767.19366666667</v>
       </c>
       <c r="J95" s="4">
         <v>11786.04</v>
@@ -5043,13 +5043,13 @@
         <v>1965.547430555556</v>
       </c>
       <c r="F98" s="4">
-        <v>1414.49</v>
+        <v>5191.89</v>
       </c>
       <c r="G98" s="4">
         <v>1026.59</v>
       </c>
       <c r="H98" s="4">
-        <v>6983.04</v>
+        <v>6158.12</v>
       </c>
       <c r="I98" s="4">
         <v>12913.09552777778</v>
@@ -5061,7 +5061,7 @@
         <v>10173.7</v>
       </c>
       <c r="L98" s="4">
-        <v>35870.64211111111</v>
+        <v>35870.64211111109</v>
       </c>
       <c r="M98" s="4">
         <v>32643.96</v>
@@ -5175,7 +5175,7 @@
         <v>488.6991</v>
       </c>
       <c r="F101" s="4">
-        <v>617</v>
+        <v>2491.85</v>
       </c>
       <c r="G101" s="4">
         <v>125.29</v>
@@ -5193,7 +5193,7 @@
         <v>3219.73</v>
       </c>
       <c r="L101" s="4">
-        <v>15477.54006111112</v>
+        <v>15477.54006111111</v>
       </c>
       <c r="M101" s="4">
         <v>12853.54</v>
@@ -5439,13 +5439,13 @@
         <v>895.3575555555556</v>
       </c>
       <c r="F107" s="4">
-        <v>1217.91</v>
+        <v>4179.93</v>
       </c>
       <c r="G107" s="4">
         <v>1551.51</v>
       </c>
       <c r="H107" s="4">
-        <v>7055.51</v>
+        <v>6154.7</v>
       </c>
       <c r="I107" s="4">
         <v>13860.647275</v>
@@ -5703,13 +5703,13 @@
         <v>848.8086111111111</v>
       </c>
       <c r="F113" s="4">
-        <v>1174.1</v>
+        <v>3557.35</v>
       </c>
       <c r="G113" s="4">
         <v>604.4</v>
       </c>
       <c r="H113" s="4">
-        <v>2417.6</v>
+        <v>2115.4</v>
       </c>
       <c r="I113" s="4">
         <v>9524.574722222223</v>
@@ -5835,13 +5835,13 @@
         <v>0</v>
       </c>
       <c r="F116" s="4">
-        <v>1193.48</v>
+        <v>4352.18</v>
       </c>
       <c r="G116" s="4">
         <v>1862.08</v>
       </c>
       <c r="H116" s="4">
-        <v>7448.32</v>
+        <v>6517.28</v>
       </c>
       <c r="I116" s="4">
         <v>2800</v>
@@ -5885,7 +5885,7 @@
         <v>0</v>
       </c>
       <c r="H117" s="5">
-        <v>0.2953686200378072</v>
+        <v>0.3375641371860654</v>
       </c>
       <c r="I117" s="5">
         <v>0.001785714285714286</v>
@@ -5967,16 +5967,16 @@
         <v>1956.945486111111</v>
       </c>
       <c r="F119" s="4">
-        <v>1960.62</v>
+        <v>6115.47</v>
       </c>
       <c r="G119" s="4">
         <v>1544.56</v>
       </c>
       <c r="H119" s="4">
-        <v>5871.71</v>
+        <v>5068.27</v>
       </c>
       <c r="I119" s="4">
-        <v>15121.16756944445</v>
+        <v>15121.16756944444</v>
       </c>
       <c r="J119" s="4">
         <v>14191.56</v>
@@ -5985,7 +5985,7 @@
         <v>12010.68</v>
       </c>
       <c r="L119" s="4">
-        <v>39650.06819444444</v>
+        <v>39650.06819444445</v>
       </c>
       <c r="M119" s="4">
         <v>39788.06</v>
@@ -6099,13 +6099,13 @@
         <v>1643.84</v>
       </c>
       <c r="F122" s="4">
-        <v>1693.56</v>
+        <v>5927.46</v>
       </c>
       <c r="G122" s="4">
         <v>1538.46</v>
       </c>
       <c r="H122" s="4">
-        <v>6318.69</v>
+        <v>5494.51</v>
       </c>
       <c r="I122" s="4">
         <v>13150.72</v>
@@ -6231,13 +6231,13 @@
         <v>821.6777777777777</v>
       </c>
       <c r="F125" s="4">
-        <v>821.6</v>
+        <v>3230.75</v>
       </c>
       <c r="G125" s="4">
         <v>1215.98</v>
       </c>
       <c r="H125" s="4">
-        <v>4355.46</v>
+        <v>3567.71</v>
       </c>
       <c r="I125" s="4">
         <v>7247.741999999999</v>
@@ -6363,13 +6363,13 @@
         <v>432.88</v>
       </c>
       <c r="F128" s="4">
-        <v>288.76</v>
+        <v>1010.66</v>
       </c>
       <c r="G128" s="4">
         <v>417.16</v>
       </c>
       <c r="H128" s="4">
-        <v>2206.45</v>
+        <v>1997.87</v>
       </c>
       <c r="I128" s="4">
         <v>3463.04</v>
@@ -6495,13 +6495,13 @@
         <v>1247.94</v>
       </c>
       <c r="F131" s="4">
-        <v>1422.42</v>
+        <v>4891.47</v>
       </c>
       <c r="G131" s="4">
         <v>1304.46</v>
       </c>
       <c r="H131" s="4">
-        <v>5410.08</v>
+        <v>4896.34</v>
       </c>
       <c r="I131" s="4">
         <v>9983.52</v>
@@ -7161,7 +7161,7 @@
         <v>420.94</v>
       </c>
       <c r="H146" s="4">
-        <v>1082.58</v>
+        <v>882.51</v>
       </c>
       <c r="I146" s="4">
         <v>425.3875666666667</v>
@@ -7284,7 +7284,7 @@
         <v>0</v>
       </c>
       <c r="E149" s="4">
-        <v>780.8736250000001</v>
+        <v>780.8736249999999</v>
       </c>
       <c r="F149" s="4">
         <v>0</v>
@@ -8035,7 +8035,7 @@
         <v>261231.33</v>
       </c>
       <c r="F167" s="4">
-        <v>370426.38</v>
+        <v>1539098.05</v>
       </c>
       <c r="G167" s="4">
         <v>194445.98</v>
@@ -8067,7 +8067,7 @@
         <v>177</v>
       </c>
       <c r="B168" s="4">
-        <v>33983.94743611111</v>
+        <v>34410.52249166667</v>
       </c>
       <c r="C168" s="4">
         <v>39305.05</v>
@@ -8076,28 +8076,28 @@
         <v>34373.06</v>
       </c>
       <c r="E168" s="4">
-        <v>68913.52768333333</v>
+        <v>69340.10273888889</v>
       </c>
       <c r="F168" s="4">
-        <v>77546.14</v>
+        <v>285698.78</v>
       </c>
       <c r="G168" s="4">
-        <v>69011.12</v>
+        <v>69011.12000000001</v>
       </c>
       <c r="H168" s="4">
-        <v>404493.35</v>
+        <v>361695.96</v>
       </c>
       <c r="I168" s="4">
-        <v>601702.5140138889</v>
+        <v>602129.0890694445</v>
       </c>
       <c r="J168" s="4">
         <v>524582.6</v>
       </c>
       <c r="K168" s="4">
-        <v>579203.92</v>
+        <v>579203.9200000002</v>
       </c>
       <c r="L168" s="4">
-        <v>1376657.880894444</v>
+        <v>1377084.45595</v>
       </c>
       <c r="M168" s="4">
         <v>1218871.32</v>
@@ -8111,7 +8111,7 @@
         <v>178</v>
       </c>
       <c r="B169" s="5">
-        <v>389.7744964707899</v>
+        <v>384.9426001365674</v>
       </c>
       <c r="C169" s="5">
         <v>457.4780594351107</v>
@@ -8120,19 +8120,19 @@
         <v>291.5461119842109</v>
       </c>
       <c r="E169" s="5">
-        <v>379.0711907833135</v>
+        <v>376.7391735540223</v>
       </c>
       <c r="F169" s="5">
-        <v>477.6851304268659</v>
+        <v>538.7135534845477</v>
       </c>
       <c r="G169" s="5">
-        <v>281.7603597796993</v>
+        <v>281.7603597796992</v>
       </c>
       <c r="H169" s="5">
-        <v>262.128878014929</v>
+        <v>293.1450713466636</v>
       </c>
       <c r="I169" s="5">
-        <v>406.0140107614058</v>
+        <v>405.7263723590416</v>
       </c>
       <c r="J169" s="5">
         <v>400.7643086141248</v>
@@ -8141,7 +8141,7 @@
         <v>238.8063585619379</v>
       </c>
       <c r="L169" s="5">
-        <v>271.0255286938704</v>
+        <v>270.9415739811002</v>
       </c>
       <c r="M169" s="5">
         <v>259.1880864011141</v>
@@ -8155,7 +8155,7 @@
         <v>179</v>
       </c>
       <c r="B170" s="4">
-        <v>98476.8125638889</v>
+        <v>98050.23750833335</v>
       </c>
       <c r="C170" s="4">
         <v>140506.93</v>
@@ -8164,28 +8164,28 @@
         <v>65840.26000000001</v>
       </c>
       <c r="E170" s="4">
-        <v>192317.8023166667</v>
+        <v>191891.2272611111</v>
       </c>
       <c r="F170" s="4">
-        <v>292880.24</v>
+        <v>1253399.27</v>
       </c>
       <c r="G170" s="4">
         <v>125434.86</v>
       </c>
       <c r="H170" s="4">
-        <v>655800.5299999998</v>
+        <v>698597.9199999999</v>
       </c>
       <c r="I170" s="4">
-        <v>1841293.995986111</v>
+        <v>1840867.420930555</v>
       </c>
       <c r="J170" s="4">
         <v>1577757.23</v>
       </c>
       <c r="K170" s="4">
-        <v>803971.87</v>
+        <v>803971.8699999999</v>
       </c>
       <c r="L170" s="4">
-        <v>2354436.419105556</v>
+        <v>2354009.84405</v>
       </c>
       <c r="M170" s="4">
         <v>1940297.93</v>
